--- a/光伏配储项目/电价数据/2026/腾飞站.xlsx
+++ b/光伏配储项目/电价数据/2026/腾飞站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.75574</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.84537</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5919500000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.72401</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.10025</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44222</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42808</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42054</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42441</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44738</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50197</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12555</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14376</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07762999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11699</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.46316</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.20154</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05153</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.8446399999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.32561</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14829</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21986</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22998</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23536</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21918</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.74761</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.26012</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44091</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.46722</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.63703</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.72892</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.97074</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7310599999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.67873</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6581399999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.31581</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.92364</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.65254</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.50021</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.73288</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.89183</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.13517</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.19142</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.66001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.26286</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86988</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79635</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7569400000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51793</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47939</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46937</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4253</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70809</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76589</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87022</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91459</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49385</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51432</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50229</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48481</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.86738</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7109</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.80621</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43594</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5087699999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50873</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7804</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99473</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5256900000000001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.89537</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.85058</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72705</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.40156</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.08798</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.03348</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47269</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5468500000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49988</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52483</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.90654</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6249400000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.89527</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.16447</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.43072</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18086</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.04113</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.47691</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.37906</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.53447</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.3135</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.36403</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.92037</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.25646</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90149</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.31882</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.36218</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.24855</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.04331</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7886299999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80852</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44889</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33459</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48723</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44802</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47184</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.57831</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.78299</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.7293099999999999</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.6624099999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5586599999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5013299999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8259299999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59637</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72748</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81551</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.53108</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5400900000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8010900000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.13247</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.67762</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.60121</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49401</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.72321</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51627</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50546</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5704400000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59604</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54471</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56471</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26423</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6161</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.20105</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.50566</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.52624</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56632</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.87259</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.90763</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.41953</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.7075499999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.73441</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.59894</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.7939400000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6099199999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.83185</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56269</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.14831</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8042</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.56055</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48376</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.50013</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34194</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52249</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49314</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44517</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.49554</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.65403</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.55028</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.7278600000000001</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.96539</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.6740499999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.7400800000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.58326</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.22528</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.06582</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.97678</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.7746499999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.20257</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.80222</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44605</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60309</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48086</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40524</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.75139</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.75987</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.6800700000000001</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.1753</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.17361</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49437</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46146</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47394</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5204800000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.8972599999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.78512</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.18888</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.8403400000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.7583300000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50038</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.69392</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.6529199999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.5735399999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41553</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.48695</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.48932</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31749</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.75517</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1.32264</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.42876</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.20299</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.46125</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.43289</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22481</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15741</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40886</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27379</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18952</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.53716</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.50784</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05532</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22453</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.45797</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.2131</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06389</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.11084</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.00429</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00321</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.06998</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48488</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34363</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.5835199999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.26351</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10278</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01617</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21795</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05512</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20933</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.07343999999999999</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07034</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33115</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31255</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45525</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78522</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.3993</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.8583</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40879</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42599</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5569299999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.40989</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70612</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87625</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46633</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5501900000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8129</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5660700000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8526900000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.62405</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.63015</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.32684</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91351</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44271</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.45965</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.19096</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25357</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27424</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.52989</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.86485</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44334</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1374</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68557</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7758200000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63724</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.50113</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.48934</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48606</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.52283</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.22271</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15556</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27399</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.008970000000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25277</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5409700000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43125</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78295</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30649</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1.32122</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.2800299999999999</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.24393</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23776</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27317</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26312</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22969</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.42452</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26168</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27776</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.49965</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45295</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33386</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48881</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.99281</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.6905399999999999</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23927</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.46628</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.46831</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42167</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.51566</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.49009</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.69038</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.7686000000000001</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7193200000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.88527</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.6496000000000001</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.9161</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.08261</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.6251599999999999</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34814</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45879</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47148</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.8190499999999999</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.94287</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.93479</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.4398</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.86382</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.50736</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.18925</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.94574</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.93002</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.15842</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.90112</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.34875</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.21788</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.25163</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.36222</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.5451</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.60265</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.32665</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.45583</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.72139</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.57881</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.46409</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.59524</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.26625</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.534</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.8882599999999999</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.70504</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.67206</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.1839</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.67932</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.6465700000000001</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.73511</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.6631</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.6575599999999999</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.16819</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.7839400000000001</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.45554</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.7635599999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.7455000000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.02046</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.51588</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>1.33008</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.51536</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>1.16471</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.503</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24006</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.36884</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.35159</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.95785</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3089</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.65388</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.95482</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.45507</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.7585299999999999</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.05256</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.30926</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.98326</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.49274</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.76163</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.75552</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3427</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.27289</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.68937</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.18217</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.51834</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.41189</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.47362</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.55522</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40691</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39579</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.47187</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41167</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.5786399999999999</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65032</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.59068</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.57626</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.8179099999999999</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.66564</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3335</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40416</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.18535</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44295</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.7396200000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.5069900000000001</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.75602</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.43357</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.59011</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.82637</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.6117100000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.65106</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.5165299999999999</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.77495</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.6759700000000001</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.11272</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.63855</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.61605</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.83209</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.6453300000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.82162</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.1608</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.1573</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.18874</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.94702</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.90486</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.22839</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.79557</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.03322</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.8053899999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.60904</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.77865</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.7916799999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.7029500000000001</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.20939</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.38296</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6838099999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34971</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45241</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5239299999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47161</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6114700000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39079</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1.39376</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41149</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49916</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.45627</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.57321</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.13989</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.18713</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.22375</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.55441</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.30337</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.66077</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.66279</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.68552</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.05665</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.81308</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.57631</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.6076699999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.59878</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.6781699999999999</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.9272100000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.93892</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.27103</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.65162</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.6563</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.6452100000000001</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.64213</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.16279</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5005299999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.61483</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.71987</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8077300000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.57908</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.70325</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.86686</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.98397</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.72323</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76463</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61736</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66562</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.06308</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.7486799999999999</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43475</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5013500000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41426</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42446</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45743</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.65742</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.6289199999999999</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.62371</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.64503</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.63409</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.9275099999999999</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.6460399999999999</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.72327</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.68264</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7333200000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.71953</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15841</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22115</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.65426</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.47361</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32904</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.45612</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.14988</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.9490599999999999</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.27271</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.26065</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.25319</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.25227</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.24654</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27928</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.24178</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18474</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24711</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27167</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26345</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25956</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25797</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03352</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19748</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25797</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24104</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27451</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.5153300000000001</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.5067200000000001</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3214</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.7615700000000001</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.26689</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28714</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.24576</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.23427</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.23731</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.23412</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.23412</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.23603</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28051</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.23049</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.23412</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.23443</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27966</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.23442</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.23422</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24118</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16059</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26611</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20757</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01224</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00032</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14551</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02115</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01539</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04073</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02922</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03836999999999999</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01912</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20123</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27911</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.23845</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32914</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.72209</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.62036</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25687</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25638</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23403</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28762</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25398</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.4357799999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.25882</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.65559</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.82196</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87566</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.84927</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12308</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21437</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25768</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01521</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00557</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06364</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25727</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4710299999999999</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.48957</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.7916299999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.7520800000000001</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7748999999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34038</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99546</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.75797</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.83608</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.78254</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83972</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8379099999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84223</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93945</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.74166</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.77849</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.74494</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3621</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46267</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.60238</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.6334</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.56459</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49291</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45726</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.27457</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45794</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46817</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44731</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.27546</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.4555</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46333</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7303099999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.60241</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46726</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33656</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42157</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.54622</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.75781</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.53944</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.53018</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.5617300000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.49317</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.46681</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.48578</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.49929</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.47546</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.46955</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.17763</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.68714</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49163</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.10319</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.95857</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.32717</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.8330700000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.20309</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.15533</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7206900000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5657799999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45369</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45191</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.69865</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.8509099999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.01218</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.51379</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45255</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41824</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23408</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3514</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45244</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.14961</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.63409</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.43265</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.67898</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.48087</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.55452</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.48181</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5137200000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.8989</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.70547</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.76595</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.24746</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.62714</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47501</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.39004</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.02398</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.24317</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.13584</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.5425</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.76224</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.7380099999999999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43902</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35579</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="P141" t="n">
+        <v>1.33187</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.22367</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>1.33695</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.46425</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.71841</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.17476</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.57708</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.98373</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.19019</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.61288</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.72868</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.28865</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.5813400000000001</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.55086</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.35646</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.67118</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.18987</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.57717</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.1774</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.39854</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.1928</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.59776</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.43039</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.47738</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.15338</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.98653</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.64366</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.28169</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.5610700000000001</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.66152</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.70504</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.68831</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.15372</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46501</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.72109</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.78215</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.6695800000000001</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.70889</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.67283</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.0694</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.45294</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.53061</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36232</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.23493</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.94687</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56231</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.95699</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.36682</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.64137</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.7955599999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.65613</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.72605</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.87512</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.67431</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.99762</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.72049</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.48092</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.6196799999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5578099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.52685</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.44681</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.46503</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.06019</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.29963</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.98442</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5401900000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.03864</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.17122</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.1001</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.8316699999999999</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.81596</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.52071</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.51524</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.45789</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.77907</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17542</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14511</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19771</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14155</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12219</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.47696</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.47974</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.67341</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.47682</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.16931</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.5196799999999999</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.7222499999999999</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.6743300000000001</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.5186499999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.68435</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.66483</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.5633400000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.50927</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.64601</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.79501</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.68938</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.6879</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.7973</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.66514</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.7029099999999999</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.7145199999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.71011</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.7835700000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.7945800000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.81892</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7631</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.35622</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.07399</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.8918200000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.68793</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.72564</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.80802</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.14744</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.46016</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.46036</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38366</v>
       </c>
     </row>
   </sheetData>
